--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12611,38 +12611,30 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="n">
+        <v>37030000</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>38573</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K182" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L182" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K182" s="5" t="n">
+        <v>37030000</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>38573</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -12651,7 +12643,7 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12686,7 +12678,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12748,7 +12740,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12810,7 +12802,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12872,7 +12864,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12934,7 +12926,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12996,7 +12988,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13058,7 +13050,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13120,7 +13112,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13322,7 +13314,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13384,7 +13376,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13446,7 +13438,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13648,7 +13640,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13710,7 +13702,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13772,7 +13764,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14036,7 +14028,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14098,7 +14090,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14300,7 +14292,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14362,7 +14354,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14424,7 +14416,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14626,7 +14618,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14688,7 +14680,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14750,7 +14742,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14952,7 +14944,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15014,7 +15006,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15076,7 +15068,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15278,7 +15270,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15340,7 +15332,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15402,7 +15394,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15604,7 +15596,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15666,7 +15658,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15728,7 +15720,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -25888,7 +25880,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25896,7 +25888,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -25911,7 +25903,7 @@
           <t>A | 1515呎 (4+房)
 $7367万
 $48,630/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25919,7 +25911,7 @@
           <t>B | 1154呎 (4+房)
 $5625万
 $48,745/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -25957,7 +25949,7 @@
           <t>A | 1515呎 (4+房)
 $6832万
 $45,098/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25965,7 +25957,7 @@
           <t>B | 1154呎 (4+房)
 $5372万
 $46,553/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -25980,7 +25972,7 @@
           <t>A | 1515呎 (4+房)
 $6785万
 $44,787/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25988,7 +25980,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -26003,7 +25995,7 @@
           <t>A | 1515呎 (4+房)
 $6801万
 $44,890/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26011,7 +26003,7 @@
           <t>B | 1154呎 (4+房)
 $5335万
 $46,231/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26064,7 @@
           <t>A | 1515呎 (4+房)
 $6600万
 $43,562/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -26080,7 +26072,7 @@
           <t>B | 1154呎 (4+房)
 $5189万
 $44,967/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -26095,7 +26087,7 @@
           <t>A | 1515呎 (4+房)
 $6554万
 $43,260/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26103,7 +26095,7 @@
           <t>B | 1154呎 (4+房)
 $5153万
 $44,657/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -26118,7 +26110,7 @@
           <t>A | 1450呎 (4+房)
 $6955万
 $47,968/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -26141,7 +26133,7 @@
           <t>A | 1450呎 (4+房)
 $6631万
 $45,728/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -26164,7 +26156,7 @@
           <t>A | 1450呎 (4+房)
 $6419万
 $44,267/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -26187,7 +26179,7 @@
           <t>A | 1515呎 (4+房)
 $6374万
 $42,074/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26195,7 +26187,7 @@
           <t>B | 1154呎 (4+房)
 $5012万
 $43,434/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26202,7 @@
           <t>A | 1515呎 (4+房)
 $6330万
 $41,783/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26218,7 +26210,7 @@
           <t>B | 1154呎 (4+房)
 $4978万
 $43,134/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -26525,7 +26517,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26535,7 +26527,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26916,7 +26908,7 @@
           <t>C | 546呎 (2房)
 $1733万
 $31,747/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26963,7 +26955,7 @@
           <t>C | 546呎 (2房)
 $1726万
 $31,621/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26994,7 +26986,7 @@
           <t>A | 960呎 (3房)
 $4234万
 $44,102/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -27002,7 +26994,7 @@
           <t>B | 960呎 (3房)
 $4196万
 $43,709/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -27018,7 +27010,7 @@
           <t>D | 484呎 (2房)
 $1516万
 $31,322/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -27041,7 +27033,7 @@
           <t>A | 960呎 (3房)
 $4205万
 $43,798/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27049,7 +27041,7 @@
           <t>B | 960呎 (3房)
 $4167万
 $43,406/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27065,7 +27057,7 @@
           <t>D | 484呎 (2房)
 $1510万
 $31,196/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27104,7 +27096,7 @@
           <t>C | 546呎 (2房)
 $1706万
 $31,244/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -27135,7 +27127,7 @@
           <t>A | 960呎 (3房)
 $3969万
 $41,342/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27143,7 +27135,7 @@
           <t>B | 960呎 (3房)
 $3934万
 $40,974/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27182,7 +27174,7 @@
           <t>A | 960呎 (3房)
 $4099万
 $42,698/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27190,7 +27182,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27229,7 +27221,7 @@
           <t>A | 960呎 (3房)
 $3941万
 $41,055/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -27237,7 +27229,7 @@
           <t>B | 960呎 (3房)
 $3906万
 $40,691/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27339,7 +27331,7 @@
           <t>C | 546呎 (2房)
 $1624万
 $29,736/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27370,7 +27362,7 @@
           <t>A | 960呎 (3房)
 $3834万
 $39,933/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -27378,7 +27370,7 @@
           <t>B | 960呎 (3房)
 $3800万
 $39,579/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -27386,7 +27378,7 @@
           <t>C | 546呎 (2房)
 $1617万
 $29,617/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27417,7 +27409,7 @@
           <t>A | 960呎 (3房)
 $3807万
 $39,657/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -27425,7 +27417,7 @@
           <t>B | 960呎 (3房)
 $3773万
 $39,306/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -27433,7 +27425,7 @@
           <t>C | 546呎 (2房)
 $1611万
 $29,500/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -27464,7 +27456,7 @@
           <t>A | 960呎 (3房)
 $3874万
 $40,351/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -27480,7 +27472,7 @@
           <t>C | 546呎 (2房)
 $1604万
 $29,383/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -27511,7 +27503,7 @@
           <t>A | 960呎 (3房)
 $3847万
 $40,070/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -27519,7 +27511,7 @@
           <t>B | 960呎 (3房)
 $3813万
 $39,715/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -27527,7 +27519,7 @@
           <t>C | 546呎 (2房)
 $1598万
 $29,264/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27535,7 +27527,7 @@
           <t>D | 484呎 (2房)
 $1409万
 $29,103/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27543,7 +27535,7 @@
           <t>E | 499呎 (2房)
 $1442万
 $28,894/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27550,7 @@
           <t>A | 960呎 (3房)
 $3878万
 $40,395/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -27566,7 +27558,7 @@
           <t>B | 960呎 (3房)
 $3844万
 $40,036/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -27574,7 +27566,7 @@
           <t>C | 546呎 (2房)
 $1669万
 $30,570/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -27600,12 +27592,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$3703万
+$38,573/呎
+(26年-07月-29日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -27613,7 +27605,7 @@
           <t>B | 960呎 (3房)
 $3670万
 $38,230/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -27621,7 +27613,7 @@
           <t>C | 546呎 (2房)
 $1663万
 $30,449/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -27652,7 +27644,7 @@
           <t>A | 960呎 (3房)
 $3703万
 $38,573/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -27660,7 +27652,7 @@
           <t>B | 960呎 (3房)
 $3823万
 $39,824/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -27668,7 +27660,7 @@
           <t>C | 546呎 (2房)
 $1585万
 $29,033/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -27676,7 +27668,7 @@
           <t>D | 484呎 (2房)
 $1397万
 $28,872/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -27684,7 +27676,7 @@
           <t>E | 499呎 (2房)
 $1430万
 $28,665/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27707,7 @@
           <t>C | 546呎 (2房)
 $1573万
 $28,802/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -27723,7 +27715,7 @@
           <t>D | 484呎 (2房)
 $1386万
 $28,643/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -27731,7 +27723,7 @@
           <t>E | 499呎 (2房)
 $1419万
 $28,439/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27754,7 @@
           <t>C | 546呎 (2房)
 $1566万
 $28,687/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -27770,7 +27762,7 @@
           <t>D | 484呎 (2房)
 $1381万
 $28,529/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -27778,7 +27770,7 @@
           <t>E | 499呎 (2房)
 $1413万
 $28,325/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27801,7 @@
           <t>C | 546呎 (2房)
 $1560万
 $28,571/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -27817,7 +27809,7 @@
           <t>D | 484呎 (2房)
 $1375万
 $28,415/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -27825,7 +27817,7 @@
           <t>E | 499呎 (2房)
 $1408万
 $28,210/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -27856,7 +27848,7 @@
           <t>C | 546呎 (2房)
 $1554万
 $28,460/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27864,7 +27856,7 @@
           <t>D | 484呎 (2房)
 $1370万
 $28,304/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -27903,7 +27895,7 @@
           <t>C | 546呎 (2房)
 $1623万
 $29,729/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27911,7 +27903,7 @@
           <t>D | 484呎 (2房)
 $1364万
 $28,190/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27919,7 +27911,7 @@
           <t>E | 499呎 (2房)
 $1397万
 $27,988/呎
-(26年-07月-10日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -27950,7 +27942,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27958,7 +27950,7 @@
           <t>D | 484呎 (2房)
 $1425万
 $29,446/呎
-(26年-06月-25日)</t>
+(26年-07月-27日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27966,7 +27958,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -27997,7 +27989,7 @@
           <t>C | 546呎 (2房)
 $1542万
 $28,233/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -28005,7 +27997,7 @@
           <t>D | 484呎 (2房)
 $1359万
 $28,076/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -28013,7 +28005,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28036,7 @@
           <t>C | 546呎 (2房)
 $1529万
 $28,011/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -28052,7 +28044,7 @@
           <t>D | 484呎 (2房)
 $1348万
 $27,853/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28060,7 +28052,7 @@
           <t>E | 499呎 (2房)
 $1380万
 $27,655/呎
-(26年-07月-10日)</t>
+(26年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28083,7 @@
           <t>C | 546呎 (2房)
 $1523万
 $27,897/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28099,7 +28091,7 @@
           <t>D | 484呎 (2房)
 $1343万
 $27,742/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28107,7 +28099,7 @@
           <t>E | 499呎 (2房)
 $1374万
 $27,545/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +132,11 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -209,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +283,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -14028,7 +14036,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14147,7 +14155,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14157,12 +14165,12 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J206" s="3" t="inlineStr">
@@ -14172,12 +14180,12 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
@@ -14187,7 +14195,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14225,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14227,12 +14235,12 @@
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J207" s="3" t="inlineStr">
@@ -14242,12 +14250,12 @@
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L207" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
@@ -14257,7 +14265,7 @@
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14473,7 +14481,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14483,12 +14491,12 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J211" s="3" t="inlineStr">
@@ -14498,12 +14506,12 @@
       </c>
       <c r="K211" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L211" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
@@ -14513,7 +14521,7 @@
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14551,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14553,12 +14561,12 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J212" s="3" t="inlineStr">
@@ -14568,12 +14576,12 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
@@ -14583,7 +14591,7 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14799,7 +14807,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14809,12 +14817,12 @@
       </c>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J216" s="3" t="inlineStr">
@@ -14824,12 +14832,12 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
@@ -14839,7 +14847,7 @@
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14869,7 +14877,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -14879,12 +14887,12 @@
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J217" s="3" t="inlineStr">
@@ -14894,12 +14902,12 @@
       </c>
       <c r="K217" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L217" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
@@ -14909,7 +14917,7 @@
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26522,22 +26530,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -27827,20 +27835,20 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -27856,7 +27864,7 @@
           <t>D | 484呎 (2房)
 $1370万
 $28,304/呎
-(26年-07月-08日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -27874,20 +27882,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -27921,20 +27929,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,11 +132,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,9 +278,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11942,7 +11934,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -13648,7 +13640,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -14155,7 +14147,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14225,7 +14217,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -14481,7 +14473,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -14551,7 +14543,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -14807,7 +14799,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14877,7 +14869,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -15604,7 +15596,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -26525,12 +26517,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -27519,7 +27511,7 @@
           <t>B | 960呎 (3房)
 $3813万
 $39,715/呎
-(26年-07月-13日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -27825,7 +27817,7 @@
           <t>E | 499呎 (2房)
 $1408万
 $28,210/呎
-(26年-07月-17日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -27835,20 +27827,20 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="24" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -27882,20 +27874,20 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -27929,20 +27921,20 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -28107,7 +28099,7 @@
           <t>E | 499呎 (2房)
 $1374万
 $27,545/呎
-(26年-07月-08日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -12425,34 +12425,34 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>17041400</v>
+        <v>13974000</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>35210</v>
+        <v>28872</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K179" s="5" t="n">
-        <v>13973948</v>
+        <v>13974000</v>
       </c>
       <c r="L179" s="5" t="n">
         <v>28872</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr">
@@ -26517,7 +26517,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26527,7 +26527,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27616,12 +27616,12 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
-$1704万
-$35,210/呎
-(在售)</t>
+$1397万
+$28,872/呎
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -123,13 +123,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -271,10 +271,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1959,38 +1959,30 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>77689000</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>51280</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K20" s="5" t="n">
+        <v>77689000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>51280</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1999,7 +1991,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2269,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2287,12 +2279,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2302,12 +2294,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2317,7 +2309,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2339,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2357,12 +2349,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -2372,12 +2364,12 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
@@ -2387,7 +2379,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2781,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2799,12 +2791,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2814,12 +2806,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2829,7 +2821,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2851,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2869,12 +2861,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2884,12 +2876,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2899,7 +2891,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2921,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2939,12 +2931,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2954,12 +2946,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -2969,7 +2961,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2991,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3009,12 +3001,12 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -3024,12 +3016,12 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -3039,7 +3031,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8105,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -8123,12 +8115,12 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
@@ -8138,12 +8130,12 @@
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
@@ -8153,7 +8145,7 @@
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8175,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
@@ -8193,12 +8185,12 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
@@ -8208,12 +8200,12 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
@@ -8223,7 +8215,7 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9002,7 +8994,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9059,7 +9051,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -9069,12 +9061,12 @@
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J126" s="3" t="inlineStr">
@@ -9084,12 +9076,12 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M126" s="3" t="inlineStr">
@@ -9099,7 +9091,7 @@
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9121,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9139,12 +9131,12 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr">
@@ -9154,12 +9146,12 @@
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
@@ -9169,7 +9161,7 @@
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10331,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10349,12 +10341,12 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
@@ -10364,12 +10356,12 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M146" s="3" t="inlineStr">
@@ -10379,7 +10371,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10401,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -10419,12 +10411,12 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
@@ -10434,12 +10426,12 @@
       </c>
       <c r="K147" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M147" s="3" t="inlineStr">
@@ -10449,7 +10441,7 @@
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10657,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
@@ -10675,12 +10667,12 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J151" s="3" t="inlineStr">
@@ -10690,12 +10682,12 @@
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M151" s="3" t="inlineStr">
@@ -10705,7 +10697,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10727,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -10745,12 +10737,12 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
@@ -10760,12 +10752,12 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M152" s="3" t="inlineStr">
@@ -10775,7 +10767,7 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12616,7 +12608,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12988,7 +12980,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -25621,7 +25613,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25631,7 +25623,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25641,7 +25633,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -25855,12 +25847,12 @@
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
+$7769万
+$51,280/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -25875,7 +25867,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $7367万
@@ -25883,7 +25875,7 @@
 (26年-06月-09日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5625万
@@ -25898,7 +25890,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $7367万
@@ -25906,7 +25898,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5625万
@@ -25921,20 +25913,20 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -25944,7 +25936,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6832万
@@ -25952,7 +25944,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5372万
@@ -25967,7 +25959,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6785万
@@ -25975,7 +25967,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5335万
@@ -25990,7 +25982,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6801万
@@ -25998,7 +25990,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5335万
@@ -26013,20 +26005,20 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -26036,20 +26028,20 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -26059,7 +26051,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6600万
@@ -26067,7 +26059,7 @@
 (26年-06月-05日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5189万
@@ -26082,7 +26074,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6554万
@@ -26090,7 +26082,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5153万
@@ -26105,7 +26097,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 1450呎 (4+房)
 $6955万
@@ -26113,7 +26105,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26128,7 +26120,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1450呎 (4+房)
 $6631万
@@ -26136,7 +26128,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26151,7 +26143,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 1450呎 (4+房)
 $6419万
@@ -26159,7 +26151,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26174,7 +26166,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6374万
@@ -26182,7 +26174,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $5012万
@@ -26197,7 +26189,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
 $6330万
@@ -26205,7 +26197,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1154呎 (4+房)
 $4978万
@@ -26289,7 +26281,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 1517呎 (4+房)
 招标单位
@@ -26297,7 +26289,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26312,7 +26304,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 1517呎 (4+房)
 招标单位
@@ -26320,7 +26312,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26335,7 +26327,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 1517呎 (4+房)
 招标单位
@@ -26343,7 +26335,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
 招标单位
@@ -26517,7 +26509,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26537,7 +26529,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -26903,7 +26895,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1733万
@@ -26911,7 +26903,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1864万
@@ -26919,7 +26911,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1908万
@@ -26934,23 +26926,23 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1726万
@@ -26958,7 +26950,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1856万
@@ -26966,7 +26958,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1900万
@@ -26981,7 +26973,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $4234万
@@ -26989,7 +26981,7 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $4196万
@@ -26997,7 +26989,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $2097万
@@ -27005,7 +26997,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1516万
@@ -27013,7 +27005,7 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1892万
@@ -27028,7 +27020,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $4205万
@@ -27036,7 +27028,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $4167万
@@ -27044,7 +27036,7 @@
 (26年-06月-23日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $2089万
@@ -27052,7 +27044,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1510万
@@ -27060,7 +27052,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1885万
@@ -27075,31 +27067,31 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1706万
 $31,244/呎
-(26年-07月-22日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1834万
@@ -27107,7 +27099,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1877万
@@ -27122,7 +27114,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3969万
@@ -27130,7 +27122,7 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3934万
@@ -27138,7 +27130,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $2072万
@@ -27146,7 +27138,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1827万
@@ -27154,7 +27146,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1870万
@@ -27169,7 +27161,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $4099万
@@ -27177,7 +27169,7 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3906万
@@ -27185,7 +27177,7 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $2064万
@@ -27193,7 +27185,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1820万
@@ -27201,7 +27193,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1862万
@@ -27216,7 +27208,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3941万
@@ -27224,7 +27216,7 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3906万
@@ -27232,7 +27224,7 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $2064万
@@ -27240,7 +27232,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1820万
@@ -27248,7 +27240,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1862万
@@ -27263,20 +27255,20 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -27310,23 +27302,23 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1624万
@@ -27334,7 +27326,7 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1745万
@@ -27342,7 +27334,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1787万
@@ -27357,7 +27349,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3834万
@@ -27365,7 +27357,7 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3800万
@@ -27373,7 +27365,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1617万
@@ -27381,7 +27373,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1738万
@@ -27389,7 +27381,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1780万
@@ -27404,7 +27396,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3807万
@@ -27412,7 +27404,7 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3773万
@@ -27420,7 +27412,7 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1611万
@@ -27428,7 +27420,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1732万
@@ -27436,7 +27428,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1772万
@@ -27451,7 +27443,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3874万
@@ -27459,7 +27451,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
@@ -27467,7 +27459,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1604万
@@ -27475,7 +27467,7 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1725万
@@ -27483,7 +27475,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1765万
@@ -27498,7 +27490,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3847万
@@ -27506,7 +27498,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3813万
@@ -27514,7 +27506,7 @@
 (26年-08月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1598万
@@ -27522,7 +27514,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1409万
@@ -27530,7 +27522,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1442万
@@ -27545,7 +27537,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3878万
@@ -27553,7 +27545,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3844万
@@ -27561,7 +27553,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1669万
@@ -27569,7 +27561,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1711万
@@ -27577,7 +27569,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1751万
@@ -27592,15 +27584,15 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3703万
 $38,573/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3670万
@@ -27608,7 +27600,7 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1663万
@@ -27616,7 +27608,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1397万
@@ -27624,7 +27616,7 @@
 (26年-08月-10日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1744万
@@ -27639,7 +27631,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 $3703万
@@ -27647,7 +27639,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 $3823万
@@ -27655,7 +27647,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1585万
@@ -27663,7 +27655,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1397万
@@ -27671,7 +27663,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1430万
@@ -27702,7 +27694,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1573万
@@ -27710,7 +27702,7 @@
 (26年-07月-14日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1386万
@@ -27718,12 +27710,12 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1419万
 $28,439/呎
-(26年-07月-18日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
     </row>
@@ -27749,7 +27741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1566万
@@ -27757,7 +27749,7 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1381万
@@ -27765,7 +27757,7 @@
 (26年-07月-10日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1413万
@@ -27796,7 +27788,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1560万
@@ -27804,7 +27796,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1375万
@@ -27812,7 +27804,7 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1408万
@@ -27827,7 +27819,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
@@ -27835,7 +27827,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
@@ -27843,7 +27835,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1554万
@@ -27851,7 +27843,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1370万
@@ -27859,7 +27851,7 @@
 (26年-08月-03日)</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1710万
@@ -27874,7 +27866,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
@@ -27882,7 +27874,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C33" s="21" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
@@ -27890,7 +27882,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1623万
@@ -27898,7 +27890,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1364万
@@ -27906,7 +27898,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1397万
@@ -27921,7 +27913,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
 招标单位
@@ -27929,7 +27921,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
 招标单位
@@ -27937,7 +27929,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1542万
@@ -27945,7 +27937,7 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1425万
@@ -27953,7 +27945,7 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1391万
@@ -27984,7 +27976,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1542万
@@ -27992,7 +27984,7 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1359万
@@ -28000,7 +27992,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1391万
@@ -28031,7 +28023,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1529万
@@ -28039,7 +28031,7 @@
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1348万
@@ -28047,7 +28039,7 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1380万
@@ -28078,7 +28070,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
 $1523万
@@ -28086,7 +28078,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1343万
@@ -28094,7 +28086,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1374万

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -2991,38 +2991,30 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>69837000</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>46097</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K36" s="5" t="n">
+        <v>69837000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>46097</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3031,7 +3023,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8175,38 +8167,30 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>43935000</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>45766</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K112" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K112" s="5" t="n">
+        <v>43935000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>45766</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -8215,7 +8199,7 @@
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10401,38 +10385,30 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="n">
+        <v>40799000</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>42499</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K147" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L147" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K147" s="5" t="n">
+        <v>40799000</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>42499</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -10441,7 +10417,7 @@
       </c>
       <c r="N147" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10727,38 +10703,30 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>40515000</v>
+      </c>
+      <c r="I152" s="5" t="n">
+        <v>42203</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K152" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K152" s="5" t="n">
+        <v>40515000</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>42203</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10767,7 +10735,7 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14578,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -25613,7 +25581,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25623,7 +25591,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26028,12 +25996,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
+$6984万
+$46,097/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -26509,7 +26477,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26519,7 +26487,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26926,12 +26894,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$4394万
+$45,766/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -27255,12 +27223,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$4080万
+$42,499/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -27302,12 +27270,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$4052万
+$42,203/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -27950,7 +27918,7 @@
           <t>E | 499呎 (2房)
 $1391万
 $27,878/呎
-(26年-07月-15日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -11571,38 +11571,30 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>38391000</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>39991</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K166" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L166" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K166" s="5" t="n">
+        <v>38391000</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>39991</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -11611,7 +11603,7 @@
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26477,7 +26469,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26487,7 +26479,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27419,12 +27411,12 @@
 (26年-06月-12日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$3839万
+$39,991/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -10633,38 +10633,30 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>40193000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>41868</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K151" s="5" t="n">
+        <v>40193000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>41868</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10673,7 +10665,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14099,38 +14091,30 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H206" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I206" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="n">
+        <v>33800000</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>35208</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K206" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L206" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K206" s="5" t="n">
+        <v>33800000</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>35208</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -14139,7 +14123,7 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26469,7 +26453,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26479,7 +26463,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27270,12 +27254,12 @@
 (26年-08月-21日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$4019万
+$41,868/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -27787,12 +27771,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$3380万
+$35,208/呎
+(26年-08月-26日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
